--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486966_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486966_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7319</v>
+        <v>2.3358</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9421</v>
+        <v>1.6941</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7899</v>
+        <v>0.6417</v>
       </c>
       <c r="G2" t="n">
         <v>-2.8631</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6567</v>
+        <v>0.2605</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2826</v>
+        <v>0.0347</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3741</v>
+        <v>0.2259</v>
       </c>
       <c r="V2" t="n">
         <v>3.2957</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9031</v>
+        <v>1.4075</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1411</v>
+        <v>3.1751</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.238</v>
+        <v>-1.7675</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.6949</v>
+        <v>0.1918</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.0003</v>
+        <v>0.9179</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3054</v>
+        <v>-0.7261</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0748</v>
+        <v>3.1715</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.1932</v>
+        <v>3.2508</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1184</v>
+        <v>-0.0793</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6201</v>
+        <v>-2.9797</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8071</v>
+        <v>-2.3329</v>
       </c>
       <c r="O3" t="n">
-        <v>0.187</v>
+        <v>-0.6468</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2321</v>
+        <v>2.2588</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2321</v>
+        <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4666</v>
+        <v>0.0658</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1461</v>
+        <v>0.0036</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3205</v>
+        <v>0.0622</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8994</v>
+        <v>-1.1088</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0698</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1704</v>
+        <v>-1.1088</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9093</v>
+        <v>1.2327</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7954</v>
+        <v>0.2559</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8861</v>
+        <v>0.9769</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1918</v>
+        <v>0.2022</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9179</v>
+        <v>0.1784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7261</v>
+        <v>0.0238</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1715</v>
+        <v>0.0389</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2508</v>
+        <v>0.0389</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0793</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9797</v>
+        <v>0.1632</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.3329</v>
+        <v>0.1395</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6468</v>
+        <v>0.0238</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2588</v>
+        <v>0.616</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2588</v>
+        <v>0.616</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4325</v>
+        <v>0.4145</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3761</v>
+        <v>0.2169</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0564</v>
+        <v>0.1976</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1088</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.905</v>
+        <v>0.7682</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0467</v>
+        <v>1.0951</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8583</v>
+        <v>-0.3269</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2022</v>
+        <v>-2.6949</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1784</v>
+        <v>-3.0003</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0238</v>
+        <v>0.3054</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0389</v>
+        <v>-1.0748</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0389</v>
+        <v>-1.1932</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1632</v>
+        <v>-1.6201</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1395</v>
+        <v>-1.8071</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0238</v>
+        <v>0.187</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0868</v>
+        <v>1.3317</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0077</v>
+        <v>1.1001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.079</v>
+        <v>0.2316</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.8994</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0698</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1704</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1681</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2837</v>
+        <v>0.0489</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4518</v>
+        <v>-0.8549</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5229</v>
+        <v>-1.0395</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8758</v>
+        <v>-0.2659</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6472</v>
+        <v>-0.7736</v>
       </c>
       <c r="J6" t="n">
-        <v>0.518</v>
+        <v>-0.1873</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0969</v>
+        <v>-0.016</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.579</v>
+        <v>-0.1713</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0409</v>
+        <v>-0.8522</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9727</v>
+        <v>-0.2498</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0682</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1967</v>
+        <v>0.3855</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9485</v>
+        <v>0.2362</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2481</v>
+        <v>0.1492</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6366</v>
+        <v>-1.1786</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.1561</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4805</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. OBIEKWE SAM</t>
+          <t>M. BETCH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9603</v>
+        <v>-0.9557</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0429</v>
+        <v>2.6273</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0826</v>
+        <v>-3.5831</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.7645</v>
+        <v>-1.3503</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6805</v>
+        <v>-2.7864</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.084</v>
+        <v>1.4361</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.5812</v>
+        <v>1.309</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5416</v>
+        <v>-0.7294</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0396</v>
+        <v>2.0385</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1833</v>
+        <v>-2.6593</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1389</v>
+        <v>-2.057</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0445</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4202</v>
+        <v>0.2508</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3248</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0954</v>
+        <v>-0.3263</v>
       </c>
       <c r="V7" t="n">
-        <v>0.768</v>
+        <v>-0.0616</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2402</v>
+        <v>1.7679</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5276999999999999</v>
+        <v>-1.8295</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>K. OBIEKWE SAM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2836</v>
+        <v>-1.4488</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3695</v>
+        <v>-2.7092</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9142</v>
+        <v>1.2604</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0395</v>
+        <v>-3.7645</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2659</v>
+        <v>-1.6805</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7736</v>
+        <v>-2.084</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1873</v>
+        <v>-2.5812</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.016</v>
+        <v>-0.5416</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1713</v>
+        <v>-2.0396</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8522</v>
+        <v>-1.1833</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2498</v>
+        <v>-1.1389</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.0445</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0922</v>
+        <v>0.9317</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1822</v>
+        <v>0.6584</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.2732</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1786</v>
+        <v>0.768</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1786</v>
+        <v>0.5276999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. BETCH</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3898</v>
+        <v>-1.6578</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1043</v>
+        <v>-2.9669</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4941</v>
+        <v>1.3091</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3503</v>
+        <v>-1.6889</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7864</v>
+        <v>1.7001</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4361</v>
+        <v>-3.3891</v>
       </c>
       <c r="J9" t="n">
-        <v>1.309</v>
+        <v>-0.1531</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7294</v>
+        <v>2.0313</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0385</v>
+        <v>-2.1844</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6593</v>
+        <v>-1.5358</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.057</v>
+        <v>-0.3311</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-1.2047</v>
       </c>
       <c r="P9" t="n">
         <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2321</v>
+        <v>2.2588</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1833</v>
+        <v>0.5239</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0541</v>
+        <v>-0.0622</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2374</v>
+        <v>0.5861</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0616</v>
+        <v>-0.6982</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7679</v>
+        <v>-0.6982</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7864</v>
+        <v>-1.882</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9218</v>
+        <v>-0.8669</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1354</v>
+        <v>-1.015</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7414</v>
+        <v>-1.5229</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3861</v>
+        <v>-0.8758</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3553</v>
+        <v>-0.6472</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2049</v>
+        <v>0.518</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0584</v>
+        <v>1.0969</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2633</v>
+        <v>-0.579</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5365</v>
+        <v>-2.0409</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4445</v>
+        <v>-1.9727</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.092</v>
+        <v>-0.0682</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5711000000000001</v>
+        <v>1.4828</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3098</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2612</v>
+        <v>0.6849</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.6366</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.1561</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8866</v>
+        <v>-2.9642</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8696</v>
+        <v>-2.9218</v>
       </c>
       <c r="F11" t="n">
-        <v>0.983</v>
+        <v>-0.0424</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6889</v>
+        <v>-2.7414</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7001</v>
+        <v>-0.3861</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.3891</v>
+        <v>-2.3553</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1531</v>
+        <v>-2.2049</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0313</v>
+        <v>0.0584</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.1844</v>
+        <v>-2.2633</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5358</v>
+        <v>-0.5365</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3311</v>
+        <v>-0.4445</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2047</v>
+        <v>-0.092</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2588</v>
+        <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7048</v>
+        <v>0.3932</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9649</v>
+        <v>0.3098</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2601</v>
+        <v>0.0834</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0657</v>
+        <v>-4.7916</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2821</v>
+        <v>-4.2748</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7836</v>
+        <v>-0.5168</v>
       </c>
       <c r="G12" t="n">
         <v>-5.8061</v>
@@ -1390,13 +1390,13 @@
         <v>2.2588</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8838</v>
+        <v>0.3903</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7364000000000001</v>
+        <v>0.2709</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1474</v>
+        <v>0.1193</v>
       </c>
       <c r="V12" t="n">
         <v>0.4189</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.091200000000001</v>
+        <v>-8.761800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.1726</v>
+        <v>-4.8432</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.9186</v>
+        <v>-3.9185</v>
       </c>
       <c r="G13" t="n">
         <v>-23.0776</v>
@@ -1456,7 +1456,7 @@
         <v>-12.9137</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.391100000000001</v>
+        <v>-4.3911</v>
       </c>
       <c r="P13" t="n">
         <v>7.186900000000001</v>
@@ -1468,22 +1468,22 @@
         <v>15.4008</v>
       </c>
       <c r="S13" t="n">
-        <v>6.101500000000001</v>
+        <v>6.4307</v>
       </c>
       <c r="T13" t="n">
-        <v>3.814000000000001</v>
+        <v>4.143400000000001</v>
       </c>
       <c r="U13" t="n">
         <v>2.2871</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6981999999999995</v>
+        <v>0.6981999999999997</v>
       </c>
       <c r="W13" t="n">
-        <v>4.999700000000001</v>
+        <v>4.9997</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.3016</v>
+        <v>-4.301600000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6151</v>
+        <v>4.1363</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9471</v>
+        <v>2.5747</v>
       </c>
       <c r="F14" t="n">
-        <v>1.668</v>
+        <v>1.5616</v>
       </c>
       <c r="G14" t="n">
         <v>3.6481</v>
@@ -1546,13 +1546,13 @@
         <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2179</v>
+        <v>0.3033</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8486</v>
+        <v>-0.221</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6307</v>
+        <v>0.5243</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0472</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0105</v>
+        <v>3.293</v>
       </c>
       <c r="E15" t="n">
-        <v>3.359</v>
+        <v>3.0452</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3484</v>
+        <v>0.2478</v>
       </c>
       <c r="G15" t="n">
         <v>2.6126</v>
@@ -1624,13 +1624,13 @@
         <v>0.4107</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8423</v>
+        <v>-0.5598</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1045</v>
+        <v>-0.2093</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9468</v>
+        <v>-0.3505</v>
       </c>
       <c r="V15" t="n">
         <v>0.8295</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4294</v>
+        <v>2.555</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9258</v>
+        <v>-0.8212</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3553</v>
+        <v>3.3762</v>
       </c>
       <c r="G16" t="n">
         <v>1.5537</v>
@@ -1702,13 +1702,13 @@
         <v>1.4374</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1613</v>
+        <v>0.2868</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1513</v>
+        <v>-0.0467</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3125</v>
+        <v>0.3334</v>
       </c>
       <c r="V16" t="n">
         <v>2.3573</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. BIESHAAR</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1337</v>
+        <v>2.1294</v>
       </c>
       <c r="E17" t="n">
-        <v>3.854</v>
+        <v>1.4871</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7203</v>
+        <v>0.6423</v>
       </c>
       <c r="G17" t="n">
-        <v>4.0589</v>
+        <v>2.1329</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6518</v>
+        <v>3.8962</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4071</v>
+        <v>-1.7633</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4315</v>
+        <v>1.471</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8404</v>
+        <v>4.445</v>
       </c>
       <c r="L17" t="n">
-        <v>3.591</v>
+        <v>-2.9741</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3726</v>
+        <v>0.6619</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1887</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1839</v>
+        <v>1.2108</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0399</v>
+        <v>-0.7632</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2357</v>
+        <v>-0.1358</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1958</v>
+        <v>-0.6274</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5277</v>
+        <v>0.3491</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7679</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>O. BIESHAAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7946</v>
+        <v>1.2933</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9055</v>
+        <v>2.9126</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1109</v>
+        <v>-1.6192</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1329</v>
+        <v>4.0589</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8962</v>
+        <v>0.6518</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7633</v>
+        <v>3.4071</v>
       </c>
       <c r="J18" t="n">
-        <v>1.471</v>
+        <v>4.4315</v>
       </c>
       <c r="K18" t="n">
-        <v>4.445</v>
+        <v>0.8404</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.9741</v>
+        <v>3.591</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6619</v>
+        <v>-0.3726</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.1887</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2108</v>
+        <v>-0.1839</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4107</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.098</v>
+        <v>0.1995</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2826</v>
+        <v>0.2943</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3806</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3491</v>
+        <v>-1.5277</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8295</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.1752</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2308</v>
+        <v>-2.127</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3241</v>
+        <v>2.3022</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8731</v>
+        <v>0.9345</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1427</v>
+        <v>-0.1525</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0158</v>
+        <v>1.087</v>
       </c>
       <c r="J19" t="n">
-        <v>0.257</v>
+        <v>-0.5927</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2175</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0395</v>
+        <v>-0.6579</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6161</v>
+        <v>1.5272</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3602</v>
+        <v>-0.2177</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9762999999999999</v>
+        <v>1.7449</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8214</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0416</v>
+        <v>-0.5191</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4611</v>
+        <v>-0.5077</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5027</v>
+        <v>-0.0114</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>I. CORRALIZA COBA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3129</v>
+        <v>0.1303</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3362</v>
+        <v>-0.2564</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0233</v>
+        <v>0.3867</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9345</v>
+        <v>4.1593</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1525</v>
+        <v>1.6963</v>
       </c>
       <c r="I20" t="n">
-        <v>1.087</v>
+        <v>2.463</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5927</v>
+        <v>2.603</v>
       </c>
       <c r="K20" t="n">
-        <v>0.06519999999999999</v>
+        <v>1.3271</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6579</v>
+        <v>1.2759</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5272</v>
+        <v>1.5563</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2177</v>
+        <v>0.3692</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7449</v>
+        <v>1.187</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0072</v>
+        <v>-0.0638</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7169</v>
+        <v>-0.0195</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2903</v>
+        <v>-0.0443</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2402</v>
+        <v>-2.117</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. CORRALIZA COBA</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4659</v>
+        <v>-0.048</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2564</v>
+        <v>-1.1262</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2096</v>
+        <v>1.0782</v>
       </c>
       <c r="G21" t="n">
-        <v>4.1593</v>
+        <v>0.8731</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6963</v>
+        <v>-0.1427</v>
       </c>
       <c r="I21" t="n">
-        <v>2.463</v>
+        <v>1.0158</v>
       </c>
       <c r="J21" t="n">
-        <v>2.603</v>
+        <v>0.257</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3271</v>
+        <v>0.2175</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2759</v>
+        <v>0.0395</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5563</v>
+        <v>0.6161</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3692</v>
+        <v>-0.3602</v>
       </c>
       <c r="O21" t="n">
-        <v>1.187</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8481</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6601</v>
+        <v>-0.0997</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0195</v>
+        <v>-0.3565</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6405999999999999</v>
+        <v>0.2568</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.117</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2068</v>
+        <v>-0.5931</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4092</v>
+        <v>-0.0954</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7976</v>
+        <v>-0.4978</v>
       </c>
       <c r="G22" t="n">
         <v>3.3044</v>
@@ -2170,13 +2170,13 @@
         <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8417</v>
+        <v>-1.2281</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.054</v>
+        <v>-0.7401</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.4879</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9997</v>
+        <v>-1.1907</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9884</v>
+        <v>-1.6746</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0112</v>
+        <v>0.4839</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1997</v>
@@ -2248,13 +2248,13 @@
         <v>0.2053</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6768</v>
+        <v>-0.8678</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6587</v>
+        <v>-0.3449</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0181</v>
+        <v>-0.5229</v>
       </c>
       <c r="V23" t="n">
         <v>0.6982</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.0913</v>
+        <v>11.8807</v>
       </c>
       <c r="E24" t="n">
-        <v>3.918800000000001</v>
+        <v>3.918799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>5.172700000000001</v>
+        <v>7.9619</v>
       </c>
       <c r="G24" t="n">
         <v>23.0778</v>
@@ -2317,7 +2317,7 @@
         <v>7.804900000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.186899999999999</v>
+        <v>-7.186900000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-15.4005</v>
@@ -2326,16 +2326,16 @@
         <v>8.213699999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.1012</v>
+        <v>-3.3119</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.2873</v>
+        <v>-2.2872</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.8141</v>
+        <v>-1.0246</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6980000000000003</v>
+        <v>-0.6979999999999998</v>
       </c>
       <c r="W24" t="n">
         <v>4.3015</v>
